--- a/data/availability/projects/mountain-view/creekview.xlsx
+++ b/data/availability/projects/mountain-view/creekview.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Typical Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -704,7 +704,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -804,7 +804,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -904,7 +904,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1159,7 +1159,6 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1216,7 +1215,6 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1273,7 +1271,6 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1330,7 +1327,6 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1387,7 +1383,6 @@
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1444,7 +1439,6 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1501,7 +1495,6 @@
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1558,7 +1551,6 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1615,7 +1607,6 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1672,7 +1663,6 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1729,7 +1719,6 @@
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1786,7 +1775,6 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1843,7 +1831,6 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1876,7 +1863,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Typical Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1900,7 +1887,6 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1933,7 +1919,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Typical Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1957,7 +1943,6 @@
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1990,7 +1975,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Typical Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2014,7 +1999,6 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2047,7 +2031,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Typical Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2071,7 +2055,6 @@
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2104,7 +2087,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Typical Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2128,7 +2111,6 @@
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2161,7 +2143,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2185,7 +2167,6 @@
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2218,7 +2199,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2242,7 +2223,6 @@
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2275,7 +2255,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2299,7 +2279,6 @@
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2332,7 +2311,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2356,7 +2335,6 @@
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2389,7 +2367,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2413,7 +2391,6 @@
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2470,7 +2447,6 @@
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2503,7 +2479,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2527,7 +2503,6 @@
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2560,7 +2535,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2584,7 +2559,6 @@
       <c r="G27" t="n">
         <v>0</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2617,7 +2591,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2641,7 +2615,6 @@
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2674,7 +2647,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2698,7 +2671,6 @@
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2755,7 +2727,6 @@
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2788,7 +2759,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2812,7 +2783,6 @@
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2845,7 +2815,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2869,7 +2839,6 @@
       <c r="G32" t="n">
         <v>0</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2902,7 +2871,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2926,7 +2895,6 @@
       <c r="G33" t="n">
         <v>0</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2959,7 +2927,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2983,7 +2951,6 @@
       <c r="G34" t="n">
         <v>0</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3016,7 +2983,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3040,7 +3007,6 @@
       <c r="G35" t="n">
         <v>0</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3073,7 +3039,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3097,7 +3063,6 @@
       <c r="G36" t="n">
         <v>0</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3130,7 +3095,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3154,7 +3119,6 @@
       <c r="G37" t="n">
         <v>0</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3187,7 +3151,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3211,7 +3175,6 @@
       <c r="G38" t="n">
         <v>0</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3244,7 +3207,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3268,7 +3231,6 @@
       <c r="G39" t="n">
         <v>0</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3325,7 +3287,6 @@
       <c r="G40" t="n">
         <v>0</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3358,7 +3319,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3382,7 +3343,6 @@
       <c r="G41" t="n">
         <v>0</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3415,7 +3375,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3439,7 +3399,6 @@
       <c r="G42" t="n">
         <v>0</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3472,7 +3431,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3496,7 +3455,6 @@
       <c r="G43" t="n">
         <v>0</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3529,7 +3487,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3553,7 +3511,6 @@
       <c r="G44" t="n">
         <v>0</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3586,7 +3543,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3610,7 +3567,6 @@
       <c r="G45" t="n">
         <v>0</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3643,7 +3599,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3667,7 +3623,6 @@
       <c r="G46" t="n">
         <v>0</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3724,7 +3679,6 @@
       <c r="G47" t="n">
         <v>0</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3757,7 +3711,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3781,7 +3735,6 @@
       <c r="G48" t="n">
         <v>0</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3838,7 +3791,6 @@
       <c r="G49" t="n">
         <v>0</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3895,7 +3847,6 @@
       <c r="G50" t="n">
         <v>47.51</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3952,7 +3903,6 @@
       <c r="G51" t="n">
         <v>41.55</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4009,7 +3959,6 @@
       <c r="G52" t="n">
         <v>0</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4042,7 +3991,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4066,7 +4015,6 @@
       <c r="G53" t="n">
         <v>0</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4099,7 +4047,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4123,7 +4071,6 @@
       <c r="G54" t="n">
         <v>0</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4180,7 +4127,6 @@
       <c r="G55" t="n">
         <v>0</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4237,7 +4183,6 @@
       <c r="G56" t="n">
         <v>0</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4294,7 +4239,6 @@
       <c r="G57" t="n">
         <v>69.40000000000001</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4327,7 +4271,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4351,7 +4295,6 @@
       <c r="G58" t="n">
         <v>0</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4408,7 +4351,6 @@
       <c r="G59" t="n">
         <v>0</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4465,7 +4407,6 @@
       <c r="G60" t="n">
         <v>58.77</v>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4498,7 +4439,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4522,7 +4463,6 @@
       <c r="G61" t="n">
         <v>0</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4555,7 +4495,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4579,7 +4519,6 @@
       <c r="G62" t="n">
         <v>0</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4612,7 +4551,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4636,7 +4575,6 @@
       <c r="G63" t="n">
         <v>0</v>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4669,7 +4607,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4693,7 +4631,6 @@
       <c r="G64" t="n">
         <v>0</v>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4726,7 +4663,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4750,7 +4687,6 @@
       <c r="G65" t="n">
         <v>0</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4783,7 +4719,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4807,7 +4743,6 @@
       <c r="G66" t="n">
         <v>0</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4864,7 +4799,6 @@
       <c r="G67" t="n">
         <v>0</v>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4921,7 +4855,6 @@
       <c r="G68" t="n">
         <v>0</v>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4978,7 +4911,6 @@
       <c r="G69" t="n">
         <v>0</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5035,7 +4967,6 @@
       <c r="G70" t="n">
         <v>118.37</v>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5092,7 +5023,6 @@
       <c r="G71" t="n">
         <v>75.89</v>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5149,7 +5079,6 @@
       <c r="G72" t="n">
         <v>0</v>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5206,7 +5135,6 @@
       <c r="G73" t="n">
         <v>75.90000000000001</v>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5263,7 +5191,6 @@
       <c r="G74" t="n">
         <v>117.69</v>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5320,7 +5247,6 @@
       <c r="G75" t="n">
         <v>0</v>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5377,7 +5303,6 @@
       <c r="G76" t="n">
         <v>0</v>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5434,7 +5359,6 @@
       <c r="G77" t="n">
         <v>63.06</v>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5491,7 +5415,6 @@
       <c r="G78" t="n">
         <v>0</v>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5548,7 +5471,6 @@
       <c r="G79" t="n">
         <v>0</v>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5605,7 +5527,6 @@
       <c r="G80" t="n">
         <v>62.15</v>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5662,7 +5583,6 @@
       <c r="G81" t="n">
         <v>0</v>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5719,7 +5639,6 @@
       <c r="G82" t="n">
         <v>0</v>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5752,7 +5671,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5776,7 +5695,6 @@
       <c r="G83" t="n">
         <v>0</v>
       </c>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5809,7 +5727,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5833,7 +5751,6 @@
       <c r="G84" t="n">
         <v>0</v>
       </c>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5866,7 +5783,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5890,7 +5807,6 @@
       <c r="G85" t="n">
         <v>0</v>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5947,7 +5863,6 @@
       <c r="G86" t="n">
         <v>0</v>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>Landscape</t>

--- a/data/availability/projects/mountain-view/creekview.xlsx
+++ b/data/availability/projects/mountain-view/creekview.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -704,7 +704,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -804,7 +804,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -854,7 +854,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sky Villa</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -904,7 +904,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sky Villa</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>I-Villa Garden</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sky Villa</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sky Villa</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sky Villa</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sky Villa</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sky Villa</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>I-Villa Garden</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>I-Villa Garden</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sky Villa</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sky Villa</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>I-Villa Garden</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Sky Villa</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>I-Villa Garden</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Sky Villa</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>I-Villa Garden</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>I-Villa Garden</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sky Villa</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>I-Villa Garden</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>I-Villa Garden</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sky Villa</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Sky Villa</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>I-Villa Garden</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Sky Villa</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Sky Villa</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>I-Villa Garden</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Sky Villa</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Sky Villa</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Sky Villa</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
